--- a/Jupyter_Notebooks_and_DataSheet_Final_Plots/Experimental_Data_All.xlsx
+++ b/Jupyter_Notebooks_and_DataSheet_Final_Plots/Experimental_Data_All.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\barna\AppData\Local\Temp\Mxt236\RemoteFiles\395372_4_5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nd4-my.sharepoint.com/personal/bagbodek_nd_edu/Documents/Documents/Research Notre Dame 2023/Thermal Conductivity IL_HFC Project/Heat_Flux_Decomposition/Structural_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7BBE38-F8A4-445E-AD0A-0C0E635DD475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="8_{9BA93234-DC9C-4D90-9BE0-9580225D52CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{556736B2-DA79-4844-9E9D-EF1900F2FCF7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{A49D4647-3304-44EA-9920-10AE1054C5FE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="3" xr2:uid="{A49D4647-3304-44EA-9920-10AE1054C5FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Experimental_TC_data" sheetId="1" r:id="rId1"/>
     <sheet name="MD_labels" sheetId="2" r:id="rId2"/>
     <sheet name="Labels_Cluster_R32" sheetId="3" r:id="rId3"/>
     <sheet name="Labels_Cluster_R134a" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="22">
   <si>
     <r>
       <t>x</t>
@@ -1185,7 +1186,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1F8734-C395-40F1-A0CF-496E25AB6AA6}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.90625" customWidth="1"/>
@@ -1258,40 +1259,6 @@
       <c r="C6" s="16">
         <v>0.96</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B10" s="16"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B11" s="16"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B12" s="16"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B13" s="16"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B14" s="16"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B15" s="16"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B16" s="16"/>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B17" s="16"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B18" s="16"/>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B19" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1377,4 +1344,106 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBAE78A4-8363-4CBD-9930-5F1AF081F9E4}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="38.81640625" customWidth="1"/>
+    <col min="2" max="2" width="26.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="16">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="16">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="16">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="16">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="16">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="16">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="16">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="16">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="16">
+        <v>0.91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>